--- a/CompareKPI_United/templates/template_J6B.xlsx
+++ b/CompareKPI_United/templates/template_J6B.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="宋体"/>
       <color theme="1"/>
@@ -146,8 +146,22 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -339,8 +353,14 @@
         <fgColor rgb="FF8EA9DB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border/>
     <border>
       <left style="thin">
@@ -513,6 +533,34 @@
         <color auto="1"/>
       </left>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1">
@@ -663,7 +711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -770,6 +818,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="38" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1781,76 +1839,76 @@
       <c r="H35" s="19" t="n"/>
     </row>
     <row r="36" s="24">
-      <c r="A36" s="27" t="n"/>
-      <c r="B36" s="0" t="inlineStr">
+      <c r="A36" s="42" t="n"/>
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>起步顿挫</t>
         </is>
       </c>
-      <c r="C36" s="28" t="n"/>
-      <c r="D36" s="0" t="inlineStr">
+      <c r="C36" s="42" t="n"/>
+      <c r="D36" s="44" t="inlineStr">
         <is>
           <t>起步1s窗口内，按顿挫规则</t>
         </is>
       </c>
-      <c r="E36" s="0" t="n"/>
-      <c r="F36" s="0" t="n"/>
-      <c r="G36" s="0" t="n"/>
-      <c r="H36" s="0" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="45" t="n"/>
+      <c r="H36" s="45" t="n"/>
     </row>
     <row r="37" s="24">
-      <c r="A37" s="27" t="n"/>
-      <c r="B37" s="0" t="inlineStr">
+      <c r="A37" s="42" t="n"/>
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>ABS触发关联ACC退出</t>
         </is>
       </c>
-      <c r="C37" s="28" t="n"/>
-      <c r="D37" s="0" t="inlineStr">
+      <c r="C37" s="42" t="n"/>
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
         </is>
       </c>
-      <c r="E37" s="0" t="n"/>
-      <c r="F37" s="0" t="n"/>
-      <c r="G37" s="0" t="n"/>
-      <c r="H37" s="0" t="n"/>
+      <c r="E37" s="45" t="n"/>
+      <c r="F37" s="45" t="n"/>
+      <c r="G37" s="45" t="n"/>
+      <c r="H37" s="45" t="n"/>
     </row>
     <row r="38" s="24">
-      <c r="A38" s="27" t="n"/>
-      <c r="B38" s="0" t="inlineStr">
+      <c r="A38" s="42" t="n"/>
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>TCS触发关联ACC退出</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="0" t="inlineStr">
+      <c r="C38" s="42" t="n"/>
+      <c r="D38" s="44" t="inlineStr">
         <is>
           <t>TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
         </is>
       </c>
-      <c r="E38" s="0" t="n"/>
-      <c r="F38" s="0" t="n"/>
-      <c r="G38" s="0" t="n"/>
-      <c r="H38" s="0" t="n"/>
+      <c r="E38" s="45" t="n"/>
+      <c r="F38" s="45" t="n"/>
+      <c r="G38" s="45" t="n"/>
+      <c r="H38" s="45" t="n"/>
     </row>
     <row r="39" s="24">
-      <c r="A39" s="27" t="n"/>
-      <c r="B39" s="0" t="inlineStr">
+      <c r="A39" s="42" t="n"/>
+      <c r="B39" s="43" t="inlineStr">
         <is>
           <t>VSE触发关联ACC退出</t>
         </is>
       </c>
-      <c r="C39" s="28" t="n"/>
-      <c r="D39" s="0" t="inlineStr">
+      <c r="C39" s="42" t="n"/>
+      <c r="D39" s="44" t="inlineStr">
         <is>
           <t>VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
         </is>
       </c>
-      <c r="E39" s="0" t="n"/>
-      <c r="F39" s="0" t="n"/>
-      <c r="G39" s="0" t="n"/>
-      <c r="H39" s="0" t="n"/>
+      <c r="E39" s="45" t="n"/>
+      <c r="F39" s="45" t="n"/>
+      <c r="G39" s="45" t="n"/>
+      <c r="H39" s="45" t="n"/>
     </row>
     <row r="40" s="24"/>
     <row r="41" s="24"/>

--- a/CompareKPI_United/templates/template_J6B.xlsx
+++ b/CompareKPI_United/templates/template_J6B.xlsx
@@ -711,7 +711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -828,6 +828,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1138,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.272727012634277" customWidth="1" style="24" min="1" max="1"/>
@@ -1271,7 +1274,7 @@
       <c r="H5" s="26" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="24">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
@@ -1839,13 +1842,13 @@
       <c r="H35" s="19" t="n"/>
     </row>
     <row r="36" s="24">
-      <c r="A36" s="42" t="n"/>
+      <c r="A36" s="28" t="n"/>
       <c r="B36" s="43" t="inlineStr">
         <is>
           <t>起步顿挫</t>
         </is>
       </c>
-      <c r="C36" s="42" t="n"/>
+      <c r="C36" s="28" t="n"/>
       <c r="D36" s="44" t="inlineStr">
         <is>
           <t>起步1s窗口内，按顿挫规则</t>
@@ -1910,30 +1913,252 @@
       <c r="G39" s="45" t="n"/>
       <c r="H39" s="45" t="n"/>
     </row>
-    <row r="40" s="24"/>
-    <row r="41" s="24"/>
-    <row r="42" s="24"/>
-    <row r="43" s="24"/>
+    <row r="40" s="24">
+      <c r="A40" s="46" t="inlineStr">
+        <is>
+          <t>行车</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>最大加速度（0-30 km/h）</t>
+        </is>
+      </c>
+      <c r="C40" s="46" t="inlineStr">
+        <is>
+          <t>行车-无干扰加速</t>
+        </is>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E40" s="45" t="n"/>
+      <c r="F40" s="45" t="n"/>
+      <c r="G40" s="45" t="n"/>
+      <c r="H40" s="45" t="n"/>
+    </row>
+    <row r="41" s="24">
+      <c r="A41" s="27" t="n"/>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>最大加速度（30-60 km/h）</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E41" s="45" t="n"/>
+      <c r="F41" s="45" t="n"/>
+      <c r="G41" s="45" t="n"/>
+      <c r="H41" s="45" t="n"/>
+    </row>
+    <row r="42" s="24">
+      <c r="A42" s="27" t="n"/>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>最大加速度（60-90 km/h）</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E42" s="45" t="n"/>
+      <c r="F42" s="45" t="n"/>
+      <c r="G42" s="45" t="n"/>
+      <c r="H42" s="45" t="n"/>
+    </row>
+    <row r="43" s="24">
+      <c r="A43" s="27" t="n"/>
+      <c r="B43" s="43" t="inlineStr">
+        <is>
+          <t>最大加速度（&gt;=90 km/h）</t>
+        </is>
+      </c>
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E43" s="45" t="n"/>
+      <c r="F43" s="45" t="n"/>
+      <c r="G43" s="45" t="n"/>
+      <c r="H43" s="45" t="n"/>
+    </row>
+    <row r="44" s="24">
+      <c r="A44" s="27" t="n"/>
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>加速建立时间（0-30 km/h）</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="n"/>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E44" s="45" t="n"/>
+      <c r="F44" s="45" t="n"/>
+      <c r="G44" s="45" t="n"/>
+      <c r="H44" s="45" t="n"/>
+    </row>
+    <row r="45" s="24">
+      <c r="A45" s="27" t="n"/>
+      <c r="B45" s="43" t="inlineStr">
+        <is>
+          <t>加速建立时间（30-60 km/h）</t>
+        </is>
+      </c>
+      <c r="C45" s="27" t="n"/>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E45" s="45" t="n"/>
+      <c r="F45" s="45" t="n"/>
+      <c r="G45" s="45" t="n"/>
+      <c r="H45" s="45" t="n"/>
+    </row>
+    <row r="46" s="24">
+      <c r="A46" s="27" t="n"/>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>加速建立时间（60-90 km/h）</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="n"/>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E46" s="45" t="n"/>
+      <c r="F46" s="45" t="n"/>
+      <c r="G46" s="45" t="n"/>
+      <c r="H46" s="45" t="n"/>
+    </row>
+    <row r="47" s="24">
+      <c r="A47" s="27" t="n"/>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>加速建立时间（&gt;=90 km/h）</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="n"/>
+      <c r="D47" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E47" s="45" t="n"/>
+      <c r="F47" s="45" t="n"/>
+      <c r="G47" s="45" t="n"/>
+      <c r="H47" s="45" t="n"/>
+    </row>
+    <row r="48" s="24">
+      <c r="A48" s="27" t="n"/>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>平均加速度（0-30 km/h）</t>
+        </is>
+      </c>
+      <c r="C48" s="27" t="n"/>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E48" s="45" t="n"/>
+      <c r="F48" s="45" t="n"/>
+      <c r="G48" s="45" t="n"/>
+      <c r="H48" s="45" t="n"/>
+    </row>
+    <row r="49" s="24">
+      <c r="A49" s="27" t="n"/>
+      <c r="B49" s="43" t="inlineStr">
+        <is>
+          <t>平均加速度（30-60 km/h）</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="n"/>
+      <c r="D49" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E49" s="45" t="n"/>
+      <c r="F49" s="45" t="n"/>
+      <c r="G49" s="45" t="n"/>
+      <c r="H49" s="45" t="n"/>
+    </row>
+    <row r="50" s="24">
+      <c r="A50" s="27" t="n"/>
+      <c r="B50" s="43" t="inlineStr">
+        <is>
+          <t>平均加速度（60-90 km/h）</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="n"/>
+      <c r="D50" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E50" s="45" t="n"/>
+      <c r="F50" s="45" t="n"/>
+      <c r="G50" s="45" t="n"/>
+      <c r="H50" s="45" t="n"/>
+    </row>
+    <row r="51" s="24">
+      <c r="A51" s="28" t="n"/>
+      <c r="B51" s="43" t="inlineStr">
+        <is>
+          <t>平均加速度（&gt;=90 km/h）</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="44" t="inlineStr">
+        <is>
+          <t>ACC 激活且无 override/前车/cut-in；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。J6B 暂无红灯/停止线信号映射，未应用该筛选。</t>
+        </is>
+      </c>
+      <c r="E51" s="45" t="n"/>
+      <c r="F51" s="45" t="n"/>
+      <c r="G51" s="45" t="n"/>
+      <c r="H51" s="45" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A40:A51"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="G2:H2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C40:C51"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="C16:C21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C24:C36"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="G3:H3"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="A6:A36"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C22:C23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CompareKPI_United/templates/template_J6B.xlsx
+++ b/CompareKPI_United/templates/template_J6B.xlsx
@@ -1385,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.27272727272727" customWidth="1" style="1" min="1" max="1"/>
@@ -1825,7 +1825,7 @@
           <t>跟车刹停风险</t>
         </is>
       </c>
-      <c r="C20" s="16" t="n"/>
+      <c r="C20" s="17" t="n"/>
       <c r="D20" s="15" t="inlineStr">
         <is>
           <t>ICE：TTC&gt;=1.5s
@@ -1842,15 +1842,19 @@
       <c r="A21" s="16" t="n"/>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>跟车刹停波动</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="n"/>
+          <t>跟车起步响应时延</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>行车-跟车起步</t>
+        </is>
+      </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>ICE：&lt;=3次
-PHEV：&lt;=3次
-BEV：&lt;=3次</t>
+          <t>ICE：&lt;=3.5s
+PHEV：&lt;=3s
+BEV：&lt;=3s</t>
         </is>
       </c>
       <c r="E21" s="12" t="n"/>
@@ -1858,43 +1862,43 @@
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
     </row>
-    <row r="22" ht="35" customHeight="1" s="1">
+    <row r="22" ht="51.5" customHeight="1" s="1">
       <c r="A22" s="16" t="n"/>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>跟车起步响应时延</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>行车-跟车起步</t>
-        </is>
-      </c>
+          <t>跟车起步舒适性</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n"/>
       <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>ICE：&lt;=3.5s
-PHEV：&lt;=3s
-BEV：&lt;=3s</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-    </row>
-    <row r="23" ht="51.5" customHeight="1" s="1">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>跟车起步舒适性</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>ICE：1.0~2m/s3
 PHEV：1.0~2m/s3
 BEV：1.0~2m/s3</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="134" customHeight="1" s="1">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>溜车</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>行车</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>ICE：ACC active，前进挡，车速&lt;=0.5kph，轮速&gt;=0.01，持续&gt;=0.20s
+PHEV：ACC active，前进挡，车速&lt;=0.5kph，轮速&gt;=0.01，持续&gt;=0.20s
+BEV：ACC active，前进挡，车速&lt;=0.5kph，轮速&gt;=0.01，持续&gt;=0.20s</t>
         </is>
       </c>
       <c r="E23" s="18" t="n"/>
@@ -1902,23 +1906,19 @@
       <c r="G23" s="18" t="n"/>
       <c r="H23" s="18" t="n"/>
     </row>
-    <row r="24" ht="134" customHeight="1" s="1">
+    <row r="24" ht="160" customHeight="1" s="1">
       <c r="A24" s="16" t="n"/>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>溜车</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>行车</t>
-        </is>
-      </c>
+          <t>无前车稳速未达到SetSpeed</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n"/>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>ICE：ACC active，前进挡，车速&lt;=0.5kph，轮速&gt;=0.01，持续&gt;=0.20s
-PHEV：ACC active，前进挡，车速&lt;=0.5kph，轮速&gt;=0.01，持续&gt;=0.20s
-BEV：ACC active，前进挡，车速&lt;=0.5kph，轮速&gt;=0.01，持续&gt;=0.20s</t>
+          <t>ICE：ACC active且无override/前车/cutin，稳定&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
+PHEV：ACC active且无override/前车/cutin，稳定&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
+BEV：ACC active且无override/前车/cutin，稳定&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed</t>
         </is>
       </c>
       <c r="E24" s="18" t="n"/>
@@ -1930,15 +1930,15 @@
       <c r="A25" s="16" t="n"/>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>无前车稳速未达到SetSpeed</t>
+          <t>不合理低速</t>
         </is>
       </c>
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override/前车/cutin，稳定&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
-PHEV：ACC active且无override/前车/cutin，稳定&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
-BEV：ACC active且无override/前车/cutin，稳定&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed</t>
+          <t>ICE：ACC active且无override/前车/cutin/曲率限速；SetSpeed波动&lt;=0.1kph，表显车速&gt;=5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
+PHEV：ACC active且无override/前车/cutin/曲率限速；SetSpeed波动&lt;=0.1kph，表显车速&gt;=5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
+BEV：ACC active且无override/前车/cutin/曲率限速；SetSpeed波动&lt;=0.1kph，表显车速&gt;=5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph</t>
         </is>
       </c>
       <c r="E25" s="18" t="n"/>
@@ -1950,15 +1950,15 @@
       <c r="A26" s="16" t="n"/>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>不合理低速</t>
+          <t>制动跳变导致的实车加速度抖动</t>
         </is>
       </c>
       <c r="C26" s="16" t="n"/>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override/前车/cutin/曲率限速；SetSpeed波动&lt;=0.1kph，表显车速&gt;=5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
-PHEV：ACC active且无override/前车/cutin/曲率限速；SetSpeed波动&lt;=0.1kph，表显车速&gt;=5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
-BEV：ACC active且无override/前车/cutin/曲率限速；SetSpeed波动&lt;=0.1kph，表显车速&gt;=5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph</t>
+          <t>ICE：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
+PHEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
+BEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2</t>
         </is>
       </c>
       <c r="E26" s="18" t="n"/>
@@ -1970,15 +1970,15 @@
       <c r="A27" s="16" t="n"/>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>制动跳变导致的实车加速度抖动</t>
+          <t>点刹</t>
         </is>
       </c>
       <c r="C27" s="16" t="n"/>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
-PHEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
-BEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2</t>
+          <t>ICE：ACC active且无override；无前车稳速或稳定跟车中制动点刹。点刹：制动扭矩短脉冲0.08~1.50s、峰值突出&gt;=180Nm、加速度下探&gt;=0.2m/s2；无前车稳速：无前车/cutin、车速&gt;5kph、稳定&gt;=8s、车速波动&lt;=2kph、SetSpeed波动&lt;=0.1kph；稳定跟车：前车有效、距离5~100m、相对速度&lt;=1.5m/s、稳定&gt;=8s、车速波动&lt;=5kph、前车距离波动&lt;=10m
+PHEV：ACC active且无override；无前车稳速或稳定跟车中制动点刹。点刹：制动扭矩短脉冲0.08~1.50s、峰值突出&gt;=180Nm、加速度下探&gt;=0.2m/s2；无前车稳速：无前车/cutin、车速&gt;5kph、稳定&gt;=8s、车速波动&lt;=2kph、SetSpeed波动&lt;=0.1kph；稳定跟车：前车有效、距离5~100m、相对速度&lt;=1.5m/s、稳定&gt;=8s、车速波动&lt;=5kph、前车距离波动&lt;=10m
+BEV：ACC active且无override；无前车稳速或稳定跟车中制动点刹。点刹：制动扭矩短脉冲0.08~1.50s、峰值突出&gt;=180Nm、加速度下探&gt;=0.2m/s2；无前车稳速：无前车/cutin、车速&gt;5kph、稳定&gt;=8s、车速波动&lt;=2kph、SetSpeed波动&lt;=0.1kph；稳定跟车：前车有效、距离5~100m、相对速度&lt;=1.5m/s、稳定&gt;=8s、车速波动&lt;=5kph、前车距离波动&lt;=10m</t>
         </is>
       </c>
       <c r="E27" s="18" t="n"/>
@@ -1990,15 +1990,15 @@
       <c r="A28" s="16" t="n"/>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>点刹</t>
+          <t>重制动</t>
         </is>
       </c>
       <c r="C28" s="16" t="n"/>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override；无前车稳速或稳定跟车中制动点刹。点刹：制动扭矩短脉冲0.08~1.50s、峰值突出&gt;=180Nm、加速度下探&gt;=0.2m/s2；无前车稳速：无前车/cutin、车速&gt;5kph、稳定&gt;=8s、车速波动&lt;=2kph、SetSpeed波动&lt;=0.1kph；稳定跟车：前车有效、距离5~100m、相对速度&lt;=1.5m/s、稳定&gt;=8s、车速波动&lt;=5kph、前车距离波动&lt;=10m
-PHEV：ACC active且无override；无前车稳速或稳定跟车中制动点刹。点刹：制动扭矩短脉冲0.08~1.50s、峰值突出&gt;=180Nm、加速度下探&gt;=0.2m/s2；无前车稳速：无前车/cutin、车速&gt;5kph、稳定&gt;=8s、车速波动&lt;=2kph、SetSpeed波动&lt;=0.1kph；稳定跟车：前车有效、距离5~100m、相对速度&lt;=1.5m/s、稳定&gt;=8s、车速波动&lt;=5kph、前车距离波动&lt;=10m
-BEV：ACC active且无override；无前车稳速或稳定跟车中制动点刹。点刹：制动扭矩短脉冲0.08~1.50s、峰值突出&gt;=180Nm、加速度下探&gt;=0.2m/s2；无前车稳速：无前车/cutin、车速&gt;5kph、稳定&gt;=8s、车速波动&lt;=2kph、SetSpeed波动&lt;=0.1kph；稳定跟车：前车有效、距离5~100m、相对速度&lt;=1.5m/s、稳定&gt;=8s、车速波动&lt;=5kph、前车距离波动&lt;=10m</t>
+          <t>ICE：ACC active且无override；加速度&lt;-2.0m/s2持续&gt;=0.20s，1.0s回看窗内减速度跳变&gt;=3.0m/s2且负向斜率&gt;=3.0m/s3，相邻事件间隔&lt;=0.50s合并
+PHEV：ACC active且无override；加速度&lt;-2.0m/s2持续&gt;=0.20s，1.0s回看窗内减速度跳变&gt;=3.0m/s2且负向斜率&gt;=3.0m/s3，相邻事件间隔&lt;=0.50s合并
+BEV：ACC active且无override；加速度&lt;-2.0m/s2持续&gt;=0.20s，1.0s回看窗内减速度跳变&gt;=3.0m/s2且负向斜率&gt;=3.0m/s3，相邻事件间隔&lt;=0.50s合并</t>
         </is>
       </c>
       <c r="E28" s="18" t="n"/>
@@ -2010,15 +2010,15 @@
       <c r="A29" s="16" t="n"/>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>重制动</t>
+          <t>顿挫</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override；加速度&lt;-2.0m/s2持续&gt;=0.20s，1.0s回看窗内减速度跳变&gt;=3.0m/s2且负向斜率&gt;=3.0m/s3，相邻事件间隔&lt;=0.50s合并
-PHEV：ACC active且无override；加速度&lt;-2.0m/s2持续&gt;=0.20s，1.0s回看窗内减速度跳变&gt;=3.0m/s2且负向斜率&gt;=3.0m/s3，相邻事件间隔&lt;=0.50s合并
-BEV：ACC active且无override；加速度&lt;-2.0m/s2持续&gt;=0.20s，1.0s回看窗内减速度跳变&gt;=3.0m/s2且负向斜率&gt;=3.0m/s3，相邻事件间隔&lt;=0.50s合并</t>
+          <t>ICE：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，车速&gt;0，候选时长&gt;0.5s且&lt;=4s，幅值&gt;=0.75，符号翻转&gt;=1，扭矩/jerk校验通过
+PHEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，车速&gt;0，候选时长&gt;0.5s且&lt;=4s，幅值&gt;=0.75，符号翻转&gt;=1，扭矩/jerk校验通过
+BEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，车速&gt;0，候选时长&gt;0.5s且&lt;=4s，幅值&gt;=0.75，符号翻转&gt;=1，扭矩/jerk校验通过</t>
         </is>
       </c>
       <c r="E29" s="18" t="n"/>
@@ -2030,15 +2030,15 @@
       <c r="A30" s="16" t="n"/>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>顿挫</t>
+          <t>Override后顿挫</t>
         </is>
       </c>
       <c r="C30" s="16" t="n"/>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>ICE：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，车速&gt;0，候选时长&gt;0.5s且&lt;=4s，幅值&gt;=0.75，符号翻转&gt;=1，扭矩/jerk校验通过
-PHEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，车速&gt;0，候选时长&gt;0.5s且&lt;=4s，幅值&gt;=0.75，符号翻转&gt;=1，扭矩/jerk校验通过
-BEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，车速&gt;0，候选时长&gt;0.5s且&lt;=4s，幅值&gt;=0.75，符号翻转&gt;=1，扭矩/jerk校验通过</t>
+          <t>ICE：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
+PHEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
+BEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数</t>
         </is>
       </c>
       <c r="E30" s="18" t="n"/>
@@ -2046,19 +2046,19 @@
       <c r="G30" s="18" t="n"/>
       <c r="H30" s="18" t="n"/>
     </row>
-    <row r="31" ht="160" customHeight="1" s="1">
+    <row r="31" ht="150.5" customHeight="1" s="1">
       <c r="A31" s="16" t="n"/>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>控制抖动</t>
+          <t>Override后重制动</t>
         </is>
       </c>
       <c r="C31" s="16" t="n"/>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>ICE：全程ACC active且车速&gt;5kph，8s内驱动/制动扭矩抖动；驱动类acc_amp&gt;=0.8m/s2，制动类acc_amp&gt;=1.45m/s2
-PHEV：全程ACC active且车速&gt;5kph，8s内驱动/制动扭矩抖动；驱动类acc_amp&gt;=0.8m/s2，制动类acc_amp&gt;=1.45m/s2
-BEV：全程ACC active且车速&gt;5kph，8s内驱动/制动扭矩抖动；驱动类acc_amp&gt;=0.8m/s2，制动类acc_amp&gt;=1.45m/s2</t>
+          <t>ICE：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
+PHEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
+BEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s</t>
         </is>
       </c>
       <c r="E31" s="18" t="n"/>
@@ -2066,19 +2066,19 @@
       <c r="G31" s="18" t="n"/>
       <c r="H31" s="18" t="n"/>
     </row>
-    <row r="32" ht="160" customHeight="1" s="1">
+    <row r="32" ht="101" customHeight="1" s="1">
       <c r="A32" s="16" t="n"/>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Override后顿挫</t>
+          <t>行车断握手</t>
         </is>
       </c>
       <c r="C32" s="16" t="n"/>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>ICE：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
-PHEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
-BEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数</t>
+          <t>ICE：ACC active且仲裁状态=2，持续&gt;=5s
+PHEV：ACC active且仲裁状态=2，持续&gt;=5s
+BEV：ACC active且仲裁状态=2，持续&gt;=5s</t>
         </is>
       </c>
       <c r="E32" s="18" t="n"/>
@@ -2090,15 +2090,15 @@
       <c r="A33" s="16" t="n"/>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Override后重制动</t>
+          <t>进Override后顿挫</t>
         </is>
       </c>
       <c r="C33" s="16" t="n"/>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>ICE：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
-PHEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
-BEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s</t>
+          <t>ICE：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
+PHEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
+BEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度</t>
         </is>
       </c>
       <c r="E33" s="18" t="n"/>
@@ -2106,59 +2106,59 @@
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="18" t="n"/>
     </row>
-    <row r="34" ht="101" customHeight="1" s="1">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>行车断握手</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>ICE：ACC active且仲裁状态=2，持续&gt;=5s
-PHEV：ACC active且仲裁状态=2，持续&gt;=5s
-BEV：ACC active且仲裁状态=2，持续&gt;=5s</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="18" t="n"/>
-      <c r="G34" s="18" t="n"/>
-      <c r="H34" s="18" t="n"/>
-    </row>
-    <row r="35" ht="150.5" customHeight="1" s="1">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>进Override后顿挫</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>ICE：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
-PHEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
-BEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-    </row>
-    <row r="36" ht="68" customHeight="1" s="1">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="21" t="inlineStr">
+    <row r="34" ht="68" customHeight="1" s="1">
+      <c r="A34" s="17" t="n"/>
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>起步顿挫</t>
         </is>
       </c>
-      <c r="C36" s="17" t="n"/>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>ICE：起步3s窗口内，按顿挫规则
 PHEV：起步1s窗口内，按顿挫规则
 BEV：起步1s窗口内，按顿挫规则</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="23" t="n"/>
+    </row>
+    <row r="35" ht="160" customHeight="1" s="1">
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>ABS触发关联ACC退出</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>ICE：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+PHEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+BEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+    </row>
+    <row r="36" ht="160" customHeight="1" s="1">
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>TCS触发关联ACC退出</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>ICE：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+PHEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+BEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
         </is>
       </c>
       <c r="E36" s="23" t="n"/>
@@ -2170,15 +2170,15 @@
       <c r="A37" s="24" t="n"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>ABS触发关联ACC退出</t>
+          <t>VSE触发关联ACC退出</t>
         </is>
       </c>
       <c r="C37" s="24" t="n"/>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>ICE：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-PHEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-BEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+          <t>ICE：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+PHEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+BEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
         </is>
       </c>
       <c r="E37" s="23" t="n"/>
@@ -2187,18 +2187,26 @@
       <c r="H37" s="23" t="n"/>
     </row>
     <row r="38" ht="160" customHeight="1" s="1">
-      <c r="A38" s="24" t="n"/>
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>行车</t>
+        </is>
+      </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>TCS触发关联ACC退出</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="n"/>
+          <t>最大加速度（0-30 km/h）</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>行车-无干扰加速</t>
+        </is>
+      </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>ICE：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-PHEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-BEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+          <t>ICE：事件最大加速度：1.5~2.5 m/s²（含边界）
+PHEV：事件最大加速度：1.5~2.5 m/s²（含边界）
+BEV：事件最大加速度：1.5~2.5 m/s²（含边界）</t>
         </is>
       </c>
       <c r="E38" s="23" t="n"/>
@@ -2207,18 +2215,18 @@
       <c r="H38" s="23" t="n"/>
     </row>
     <row r="39" ht="160" customHeight="1" s="1">
-      <c r="A39" s="24" t="n"/>
+      <c r="A39" s="16" t="n"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>VSE触发关联ACC退出</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="n"/>
+          <t>最大加速度（30-60 km/h）</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n"/>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>ICE：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-PHEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-BEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+          <t>ICE：事件最大加速度：1.5~2.5 m/s²（含边界）
+PHEV：事件最大加速度：1.5~2.5 m/s²（含边界）
+BEV：事件最大加速度：1.5~2.5 m/s²（含边界）</t>
         </is>
       </c>
       <c r="E39" s="23" t="n"/>
@@ -2227,21 +2235,13 @@
       <c r="H39" s="23" t="n"/>
     </row>
     <row r="40" ht="160" customHeight="1" s="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>行车</t>
-        </is>
-      </c>
+      <c r="A40" s="16" t="n"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>最大加速度（0-30 km/h）</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="inlineStr">
-        <is>
-          <t>行车-无干扰加速</t>
-        </is>
-      </c>
+          <t>最大加速度（60-90 km/h）</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n"/>
       <c r="D40" s="22" t="inlineStr">
         <is>
           <t>ICE：事件最大加速度：1.5~2.5 m/s²（含边界）
@@ -2258,7 +2258,7 @@
       <c r="A41" s="16" t="n"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>最大加速度（30-60 km/h）</t>
+          <t>最大加速度（&gt;=90 km/h）</t>
         </is>
       </c>
       <c r="C41" s="16" t="n"/>
@@ -2278,15 +2278,15 @@
       <c r="A42" s="16" t="n"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>最大加速度（60-90 km/h）</t>
+          <t>加速建立时间（0-30 km/h）</t>
         </is>
       </c>
       <c r="C42" s="16" t="n"/>
       <c r="D42" s="22" t="inlineStr">
         <is>
-          <t>ICE：事件最大加速度：1.5~2.5 m/s²（含边界）
-PHEV：事件最大加速度：1.5~2.5 m/s²（含边界）
-BEV：事件最大加速度：1.5~2.5 m/s²（含边界）</t>
+          <t>ICE：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
+PHEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
+BEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s</t>
         </is>
       </c>
       <c r="E42" s="23" t="n"/>
@@ -2298,15 +2298,15 @@
       <c r="A43" s="16" t="n"/>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>最大加速度（&gt;=90 km/h）</t>
+          <t>加速建立时间（30-60 km/h）</t>
         </is>
       </c>
       <c r="C43" s="16" t="n"/>
       <c r="D43" s="22" t="inlineStr">
         <is>
-          <t>ICE：事件最大加速度：1.5~2.5 m/s²（含边界）
-PHEV：事件最大加速度：1.5~2.5 m/s²（含边界）
-BEV：事件最大加速度：1.5~2.5 m/s²（含边界）</t>
+          <t>ICE：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
+PHEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
+BEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s</t>
         </is>
       </c>
       <c r="E43" s="23" t="n"/>
@@ -2318,7 +2318,7 @@
       <c r="A44" s="16" t="n"/>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>加速建立时间（0-30 km/h）</t>
+          <t>加速建立时间（60-90 km/h）</t>
         </is>
       </c>
       <c r="C44" s="16" t="n"/>
@@ -2338,7 +2338,7 @@
       <c r="A45" s="16" t="n"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>加速建立时间（30-60 km/h）</t>
+          <t>加速建立时间（&gt;=90 km/h）</t>
         </is>
       </c>
       <c r="C45" s="16" t="n"/>
@@ -2358,15 +2358,15 @@
       <c r="A46" s="16" t="n"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>加速建立时间（60-90 km/h）</t>
+          <t>平均加速度（0-30 km/h）</t>
         </is>
       </c>
       <c r="C46" s="16" t="n"/>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>ICE：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
-PHEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
-BEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s</t>
+          <t>ICE：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
+PHEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
+BEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²</t>
         </is>
       </c>
       <c r="E46" s="23" t="n"/>
@@ -2378,15 +2378,15 @@
       <c r="A47" s="16" t="n"/>
       <c r="B47" s="21" t="inlineStr">
         <is>
-          <t>加速建立时间（&gt;=90 km/h）</t>
+          <t>平均加速度（30-60 km/h）</t>
         </is>
       </c>
       <c r="C47" s="16" t="n"/>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>ICE：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
-PHEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
-BEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s</t>
+          <t>ICE：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
+PHEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
+BEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²</t>
         </is>
       </c>
       <c r="E47" s="23" t="n"/>
@@ -2398,7 +2398,7 @@
       <c r="A48" s="16" t="n"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>平均加速度（0-30 km/h）</t>
+          <t>平均加速度（60-90 km/h）</t>
         </is>
       </c>
       <c r="C48" s="16" t="n"/>
@@ -2415,13 +2415,13 @@
       <c r="H48" s="23" t="n"/>
     </row>
     <row r="49" ht="160" customHeight="1" s="1">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="17" t="n"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
-          <t>平均加速度（30-60 km/h）</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="n"/>
+          <t>平均加速度（&gt;=90 km/h）</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="n"/>
       <c r="D49" s="22" t="inlineStr">
         <is>
           <t>ICE：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
@@ -2434,67 +2434,27 @@
       <c r="G49" s="23" t="n"/>
       <c r="H49" s="23" t="n"/>
     </row>
-    <row r="50" ht="160" customHeight="1" s="1">
-      <c r="A50" s="16" t="n"/>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>平均加速度（60-90 km/h）</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="22" t="inlineStr">
-        <is>
-          <t>ICE：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
-PHEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
-BEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="n"/>
-      <c r="F50" s="23" t="n"/>
-      <c r="G50" s="23" t="n"/>
-      <c r="H50" s="23" t="n"/>
-    </row>
-    <row r="51" ht="160" customHeight="1" s="1">
-      <c r="A51" s="17" t="n"/>
-      <c r="B51" s="21" t="inlineStr">
-        <is>
-          <t>平均加速度（&gt;=90 km/h）</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="n"/>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>ICE：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
-PHEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
-BEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="23" t="n"/>
-      <c r="G51" s="23" t="n"/>
-      <c r="H51" s="23" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A38:A49"/>
+    <mergeCell ref="C23:C34"/>
+    <mergeCell ref="C38:C49"/>
+    <mergeCell ref="A6:A34"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="A40:A51"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E5:H5"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E5:H5"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C40:C51"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C16:C20"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C24:C36"/>
     <mergeCell ref="C6:C9"/>
-    <mergeCell ref="A6:A36"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CompareKPI_United/templates/template_J6B.xlsx
+++ b/CompareKPI_United/templates/template_J6B.xlsx
@@ -1596,9 +1596,9 @@
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>ICE：首次acc&gt;0.2到最大acc：1.0~4.5s
-PHEV：首次acc&gt;0.2到最大acc：1.0~4.0s
-BEV：首次acc&gt;0.2到最大acc：1.0~4.0s</t>
+          <t>ICE：&lt;=4.5s
+PHEV：&lt;=4s
+BEV：&lt;=4s</t>
         </is>
       </c>
       <c r="E9" s="12" t="n"/>
@@ -1684,9 +1684,9 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>ICE：速度波动&lt;=±0.6m/s
-PHEV：速度波动&lt;=±0.3m/s
-BEV：速度波动&lt;=±0.3m/s</t>
+          <t>ICE：车速半极差&lt;=0.6m/s
+PHEV：车速半极差&lt;=0.3m/s
+BEV：车速半极差&lt;=0.3m/s</t>
         </is>
       </c>
       <c r="E13" s="12" t="n"/>
@@ -1704,9 +1704,9 @@
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>ICE：|加速度|&lt;=1.0m/s2
-PHEV：|加速度|&lt;=1.0m/s2
-BEV：|加速度|&lt;=1.0m/s2</t>
+          <t>ICE：|加速度|&lt;=1m/s2
+PHEV：|加速度|&lt;=1m/s2
+BEV：|加速度|&lt;=1m/s2</t>
         </is>
       </c>
       <c r="E14" s="12" t="n"/>
@@ -1768,9 +1768,9 @@
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>ICE：刹停完成时距前车距离：2.5~4.5m
-PHEV：刹停完成时距前车距离：3~4m
-BEV：刹停完成时距前车距离：3~4m</t>
+          <t>ICE：2.5~4.5m
+PHEV：3~4m
+BEV：3~4m</t>
         </is>
       </c>
       <c r="E17" s="12" t="n"/>
@@ -1872,9 +1872,9 @@
       <c r="C22" s="17" t="n"/>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>ICE：1.0~2m/s3
-PHEV：1.0~2m/s3
-BEV：1.0~2m/s3</t>
+          <t>ICE：最大jerk&lt;=2m/s3
+PHEV：最大jerk&lt;=2m/s3
+BEV：最大jerk&lt;=2m/s3</t>
         </is>
       </c>
       <c r="E22" s="18" t="n"/>
@@ -2441,7 +2441,6 @@
     <mergeCell ref="A38:A49"/>
     <mergeCell ref="C23:C34"/>
     <mergeCell ref="C38:C49"/>
-    <mergeCell ref="A6:A34"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="C21:C22"/>
@@ -2454,6 +2453,7 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C16:C20"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:A34"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
